--- a/exports/UPL_full_report.xlsx
+++ b/exports/UPL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.27</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.38541666666</v>
+        <v>44579.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>779.65</v>
+        <v>765.5</v>
       </c>
       <c r="I2" t="n">
         <v>770.9818564944501</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.54</v>
+        <v>-2.35</v>
       </c>
       <c r="L2" t="n">
         <v>3.09</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.77</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44622.38541666666</v>
+        <v>44622.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>658.7</v>
+        <v>660.9</v>
       </c>
       <c r="I3" t="n">
         <v>659.020239402273</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>42.83333333333334</v>
+        <v>43</v>
       </c>
       <c r="K3" t="n">
-        <v>13.95</v>
+        <v>13.66</v>
       </c>
       <c r="L3" t="n">
         <v>3.12</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44651.38541666666</v>
+        <v>44651.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>738.75</v>
+        <v>736.75</v>
       </c>
       <c r="I4" t="n">
         <v>737.8638136843743</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K4" t="n">
-        <v>11.78</v>
+        <v>11.48</v>
       </c>
       <c r="L4" t="n">
         <v>1.44</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>4.51</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44656.55208333334</v>
+        <v>44657.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>762.6</v>
+        <v>773.25</v>
       </c>
       <c r="I5" t="n">
         <v>769.9604766084448</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.51</v>
+        <v>-4.95</v>
       </c>
       <c r="L5" t="n">
-        <v>4.22</v>
+        <v>5.68</v>
       </c>
       <c r="M5" t="n">
         <v>0.82</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>4.84</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>790.15</v>
+        <v>749.6</v>
       </c>
       <c r="I6" t="n">
         <v>762.3917866308955</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>2.19</v>
+        <v>-3.06</v>
       </c>
       <c r="L6" t="n">
-        <v>1.94</v>
+        <v>3.3</v>
       </c>
       <c r="M6" t="n">
         <v>2.63</v>
       </c>
       <c r="N6" t="n">
-        <v>2.69</v>
+        <v>4.37</v>
       </c>
       <c r="O6" t="n">
         <v>1.12</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.93</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44748.55208333334</v>
+        <v>44749.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>636</v>
+        <v>654.4</v>
       </c>
       <c r="I7" t="n">
         <v>639.1497201937153</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K7" t="n">
-        <v>15.15</v>
+        <v>12.7</v>
       </c>
       <c r="L7" t="n">
         <v>5.94</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.13</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>736.5</v>
+        <v>723.7</v>
       </c>
       <c r="I8" t="n">
         <v>728.616750129838</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K8" t="n">
-        <v>12.55</v>
+        <v>10.59</v>
       </c>
       <c r="L8" t="n">
         <v>2.8</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>4.87</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44853.55208333334</v>
+        <v>44854.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>648.85</v>
+        <v>668.6</v>
       </c>
       <c r="I9" t="n">
         <v>668.126168590678</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K9" t="n">
-        <v>10.34</v>
+        <v>7.61</v>
       </c>
       <c r="L9" t="n">
         <v>3.25</v>
@@ -954,7 +1061,7 @@
         <v>2.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.89</v>
+        <v>5.33</v>
       </c>
       <c r="O9" t="n">
         <v>-2.9</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.32</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>746.2</v>
+        <v>732.1</v>
       </c>
       <c r="I10" t="n">
         <v>738.8442440731698</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K10" t="n">
-        <v>11.61</v>
+        <v>9.5</v>
       </c>
       <c r="L10" t="n">
         <v>4.32</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>5.36</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44944.55208333334</v>
+        <v>44945.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>703.15</v>
+        <v>715.55</v>
       </c>
       <c r="I11" t="n">
         <v>709.0806421406505</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K11" t="n">
-        <v>3.95</v>
+        <v>2.26</v>
       </c>
       <c r="L11" t="n">
         <v>3.05</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>4.75</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44958.55208333334</v>
+        <v>44959.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>709.85</v>
+        <v>670.9</v>
       </c>
       <c r="I12" t="n">
         <v>695.1230125006686</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8</v>
+        <v>-6.24</v>
       </c>
       <c r="L12" t="n">
-        <v>2.14</v>
+        <v>8.27</v>
       </c>
       <c r="M12" t="n">
         <v>0.14</v>
       </c>
       <c r="N12" t="n">
-        <v>1.37</v>
+        <v>5.55</v>
       </c>
       <c r="O12" t="n">
         <v>2.06</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>9.09</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44970.55208333334</v>
+        <v>44971.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>702.95</v>
+        <v>725.85</v>
       </c>
       <c r="I13" t="n">
         <v>713.6145738870126</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.78</v>
+        <v>-8.19</v>
       </c>
       <c r="L13" t="n">
-        <v>5.95</v>
+        <v>9.58</v>
       </c>
       <c r="M13" t="n">
-        <v>0.32</v>
+        <v>0.51</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
         <v>-5.55</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>6.12</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>708.9</v>
+        <v>678.75</v>
       </c>
       <c r="I14" t="n">
         <v>707.244135080567</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.34</v>
+        <v>-6.49</v>
       </c>
       <c r="L14" t="n">
-        <v>2.73</v>
+        <v>6.75</v>
       </c>
       <c r="M14" t="n">
         <v>1.35</v>
       </c>
       <c r="N14" t="n">
-        <v>1.88</v>
+        <v>4.27</v>
       </c>
       <c r="O14" t="n">
         <v>3.75</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.51</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>694.9</v>
+        <v>699.85</v>
       </c>
       <c r="I15" t="n">
         <v>698.2577365898329</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.38</v>
+        <v>-3.11</v>
       </c>
       <c r="L15" t="n">
         <v>4.29</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>4.52</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45040.55208333334</v>
+        <v>45041.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>699.95</v>
+        <v>684.35</v>
       </c>
       <c r="I16" t="n">
         <v>686.1204300961042</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01</v>
+        <v>-2.21</v>
       </c>
       <c r="L16" t="n">
-        <v>0.88</v>
+        <v>2.79</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04</v>
+        <v>1.34</v>
       </c>
       <c r="N16" t="n">
-        <v>1.05</v>
+        <v>1.94</v>
       </c>
       <c r="O16" t="n">
         <v>1.74</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>3.99</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45044.38541666666</v>
+        <v>45044.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>707.9</v>
+        <v>709.05</v>
       </c>
       <c r="I17" t="n">
         <v>708.038072968458</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.44</v>
+        <v>-3.61</v>
       </c>
       <c r="L17" t="n">
-        <v>3.86</v>
+        <v>3.99</v>
       </c>
       <c r="M17" t="n">
         <v>0.67</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>3.71</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45050.55208333334</v>
+        <v>45051.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>701.85</v>
+        <v>690.65</v>
       </c>
       <c r="I18" t="n">
         <v>694.0599317247129</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.02</v>
+        <v>-2.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.49</v>
+        <v>2.86</v>
       </c>
       <c r="M18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>1.52</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.16</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45082.55208333334</v>
+        <v>45083.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>661.9</v>
+        <v>665.35</v>
       </c>
       <c r="I19" t="n">
         <v>662.7608432728068</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K19" t="n">
-        <v>4.16</v>
+        <v>3.66</v>
       </c>
       <c r="L19" t="n">
         <v>2.1</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>2.55</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45099.38541666666</v>
+        <v>45099.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>652.05</v>
+        <v>647</v>
       </c>
       <c r="I20" t="n">
         <v>651.2396396677967</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-2</v>
+        <v>-2.76</v>
       </c>
       <c r="L20" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
         <v>0.54</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>3.28</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45166.55208333334</v>
+        <v>45167.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>561.2</v>
+        <v>574.85</v>
       </c>
       <c r="I21" t="n">
         <v>574.2484479234686</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>67</v>
+        <v>67.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>13.26</v>
+        <v>11.15</v>
       </c>
       <c r="L21" t="n">
         <v>2.14</v>
@@ -1638,7 +1889,7 @@
         <v>0.86</v>
       </c>
       <c r="N21" t="n">
-        <v>1.83</v>
+        <v>2.46</v>
       </c>
       <c r="O21" t="n">
         <v>-1.81</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45196.55208333334</v>
+        <v>45197.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>590.15</v>
+        <v>586.1</v>
       </c>
       <c r="I22" t="n">
         <v>586.7339850090214</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K22" t="n">
-        <v>2.66</v>
+        <v>1.96</v>
       </c>
       <c r="L22" t="n">
         <v>1.71</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>4.46</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>596.15</v>
+        <v>601.75</v>
       </c>
       <c r="I23" t="n">
         <v>599.6500196398456</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.71</v>
+        <v>-2.67</v>
       </c>
       <c r="L23" t="n">
-        <v>2.37</v>
+        <v>3.05</v>
       </c>
       <c r="M23" t="n">
         <v>1.12</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>3.87</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>588</v>
+        <v>579.85</v>
       </c>
       <c r="I24" t="n">
         <v>585.3359239228627</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.29</v>
+        <v>-3.64</v>
       </c>
       <c r="L24" t="n">
-        <v>3.19</v>
+        <v>3.64</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="O24" t="n">
         <v>1.05</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>4.2</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>530.95</v>
+        <v>540.2</v>
       </c>
       <c r="I25" t="n">
         <v>538.6328905451861</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K25" t="n">
-        <v>8.43</v>
+        <v>6.84</v>
       </c>
       <c r="L25" t="n">
         <v>1.41</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>567.05</v>
+        <v>547.8</v>
       </c>
       <c r="I26" t="n">
         <v>564.9516979782763</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>4.97</v>
+        <v>1.41</v>
       </c>
       <c r="L26" t="n">
         <v>1.48</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.52</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45337.55208333334</v>
+        <v>45338.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>468.5</v>
+        <v>471.65</v>
       </c>
       <c r="I27" t="n">
         <v>468.7327585529079</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>57</v>
+        <v>57.83333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>14.48</v>
+        <v>13.9</v>
       </c>
       <c r="L27" t="n">
         <v>5.73</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>6.85</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45350.38541666666</v>
+        <v>45350.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>459.95</v>
+        <v>455.05</v>
       </c>
       <c r="I28" t="n">
         <v>455.4333707351606</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.48</v>
+        <v>-3.52</v>
       </c>
       <c r="L28" t="n">
-        <v>2.48</v>
+        <v>3.59</v>
       </c>
       <c r="M28" t="n">
         <v>0.9</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>5.24</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45385.55208333334</v>
+        <v>45386.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>458.45</v>
+        <v>474.25</v>
       </c>
       <c r="I29" t="n">
         <v>459.4092740818146</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.75</v>
+        <v>-4.22</v>
       </c>
       <c r="L29" t="n">
-        <v>3.52</v>
+        <v>4.24</v>
       </c>
       <c r="M29" t="n">
         <v>0.86</v>
       </c>
       <c r="N29" t="n">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="O29" t="n">
         <v>-2.17</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.98</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>474.15</v>
+        <v>463.8</v>
       </c>
       <c r="I30" t="n">
         <v>468.7555960379784</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.02</v>
+        <v>-2.2</v>
       </c>
       <c r="L30" t="n">
         <v>5.63</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>6.49</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45422.38541666666</v>
+        <v>45422.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>459.3</v>
+        <v>480.6</v>
       </c>
       <c r="I31" t="n">
         <v>473.3007769641908</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>0.97</v>
+        <v>-3.62</v>
       </c>
       <c r="L31" t="n">
-        <v>3.06</v>
+        <v>4.44</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>8.67</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>508.4</v>
+        <v>480.7</v>
       </c>
       <c r="I32" t="n">
         <v>480.7168894543488</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>5.78</v>
+        <v>0.02</v>
       </c>
       <c r="L32" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="M32" t="n">
         <v>2.2</v>
       </c>
       <c r="N32" t="n">
-        <v>5.24</v>
+        <v>5.85</v>
       </c>
       <c r="O32" t="n">
         <v>7.49</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45449.38541666666</v>
+        <v>45449.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>507.45</v>
+        <v>517.05</v>
       </c>
       <c r="I33" t="n">
         <v>516.5555695419774</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.56</v>
+        <v>-7.56</v>
       </c>
       <c r="L33" t="n">
         <v>8.85</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.9</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>535.95</v>
+        <v>523.35</v>
       </c>
       <c r="I34" t="n">
         <v>526.1469808557704</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K34" t="n">
-        <v>3.66</v>
+        <v>1.22</v>
       </c>
       <c r="L34" t="n">
         <v>1.91</v>
@@ -2379,7 +2786,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>1.12</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
         <v>2.28</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>5.69</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45499.55208333334</v>
+        <v>45502.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>522.3</v>
+        <v>537</v>
       </c>
       <c r="I35" t="n">
         <v>536.7552999162672</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2</v>
+        <v>-2.61</v>
       </c>
       <c r="L35" t="n">
-        <v>2.68</v>
+        <v>3.83</v>
       </c>
       <c r="M35" t="n">
-        <v>0.34</v>
+        <v>0.65</v>
       </c>
       <c r="N35" t="n">
         <v>2.6</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>6.58</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45506.38541666666</v>
+        <v>45506.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>537.15</v>
+        <v>511.3</v>
       </c>
       <c r="I36" t="n">
         <v>520.5531636695813</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>0.03</v>
+        <v>-4.79</v>
       </c>
       <c r="L36" t="n">
-        <v>2.56</v>
+        <v>5.07</v>
       </c>
       <c r="M36" t="n">
         <v>1.06</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>9.84</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45525.55208333334</v>
+        <v>45526.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>545.8</v>
+        <v>553.4</v>
       </c>
       <c r="I37" t="n">
         <v>547.7753219962741</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.75</v>
+        <v>-8.23</v>
       </c>
       <c r="L37" t="n">
-        <v>7.46</v>
+        <v>10.3</v>
       </c>
       <c r="M37" t="n">
         <v>1.96</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>4.86</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>580.25</v>
+        <v>562.4</v>
       </c>
       <c r="I38" t="n">
         <v>567.3132263962776</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K38" t="n">
-        <v>4.85</v>
+        <v>1.63</v>
       </c>
       <c r="L38" t="n">
         <v>1.5</v>
@@ -2607,7 +3062,7 @@
         <v>0.57</v>
       </c>
       <c r="N38" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="O38" t="n">
         <v>1.85</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>6.96</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45565.55208333334</v>
+        <v>45566.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>587.05</v>
+        <v>596.65</v>
       </c>
       <c r="I39" t="n">
         <v>591.9678553794614</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.38</v>
+        <v>-6.09</v>
       </c>
       <c r="L39" t="n">
-        <v>5.39</v>
+        <v>6.61</v>
       </c>
       <c r="M39" t="n">
         <v>0.37</v>
       </c>
       <c r="N39" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="O39" t="n">
         <v>-1.83</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>5.3</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>576.15</v>
+        <v>556.9</v>
       </c>
       <c r="I40" t="n">
         <v>570.6884686304861</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.44</v>
+        <v>-6.66</v>
       </c>
       <c r="L40" t="n">
-        <v>4.08</v>
+        <v>7.13</v>
       </c>
       <c r="M40" t="n">
         <v>0.49</v>
       </c>
       <c r="N40" t="n">
-        <v>2.71</v>
+        <v>3.44</v>
       </c>
       <c r="O40" t="n">
         <v>1.62</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45596.38541666666</v>
+        <v>45596.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>524.2</v>
+        <v>531.4</v>
       </c>
       <c r="I41" t="n">
         <v>530.5341629768343</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>5.87</v>
+        <v>4.58</v>
       </c>
       <c r="L41" t="n">
         <v>4.29</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.23</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>532.5</v>
+        <v>509.45</v>
       </c>
       <c r="I42" t="n">
         <v>515.8984274972835</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>0.21</v>
+        <v>-4.13</v>
       </c>
       <c r="L42" t="n">
-        <v>2.56</v>
+        <v>4.68</v>
       </c>
       <c r="M42" t="n">
         <v>0.61</v>
       </c>
       <c r="N42" t="n">
-        <v>2.27</v>
+        <v>7.53</v>
       </c>
       <c r="O42" t="n">
         <v>1.68</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>8.67</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45615.55208333334</v>
+        <v>45617.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>523.25</v>
+        <v>538.1</v>
       </c>
       <c r="I43" t="n">
         <v>537.5780620471292</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.71</v>
+        <v>-5.62</v>
       </c>
       <c r="L43" t="n">
-        <v>4.6</v>
+        <v>6.06</v>
       </c>
       <c r="M43" t="n">
         <v>3.25</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.04</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45643.38541666666</v>
+        <v>45643.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>542.4</v>
+        <v>537</v>
       </c>
       <c r="I44" t="n">
         <v>537.5314577432658</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="L44" t="n">
         <v>4.3</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.15</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>508.95</v>
+        <v>529</v>
       </c>
       <c r="I45" t="n">
         <v>523.0048346760959</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>5.22</v>
+        <v>1.49</v>
       </c>
       <c r="L45" t="n">
         <v>1.28</v>
@@ -3006,7 +3545,7 @@
         <v>0.44</v>
       </c>
       <c r="N45" t="n">
-        <v>1.43</v>
+        <v>4.19</v>
       </c>
       <c r="O45" t="n">
         <v>-1.83</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>7.07</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45719.55208333334</v>
+        <v>45720.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>615.45</v>
+        <v>610.25</v>
       </c>
       <c r="I46" t="n">
         <v>615.1571050583341</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K46" t="n">
-        <v>16.34</v>
+        <v>15.36</v>
       </c>
       <c r="L46" t="n">
         <v>3.88</v>
       </c>
       <c r="M46" t="n">
-        <v>0.99</v>
+        <v>1.37</v>
       </c>
       <c r="N46" t="n">
         <v>3.74</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>7.05</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>634</v>
+        <v>646.25</v>
       </c>
       <c r="I47" t="n">
         <v>638.9362965879409</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.89</v>
+        <v>-5.9</v>
       </c>
       <c r="L47" t="n">
-        <v>5.32</v>
+        <v>6.19</v>
       </c>
       <c r="M47" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N47" t="n">
         <v>3.89</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.94</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45743.55208333334</v>
+        <v>45744.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>656</v>
+        <v>630.25</v>
       </c>
       <c r="I48" t="n">
         <v>630.5891545884875</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K48" t="n">
-        <v>1.51</v>
+        <v>-2.48</v>
       </c>
       <c r="L48" t="n">
-        <v>1.45</v>
+        <v>2.93</v>
       </c>
       <c r="M48" t="n">
         <v>0.08</v>
       </c>
       <c r="N48" t="n">
-        <v>1.2</v>
+        <v>3.12</v>
       </c>
       <c r="O48" t="n">
         <v>1.95</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.1</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>651.95</v>
+        <v>659.3</v>
       </c>
       <c r="I49" t="n">
         <v>655.8024006965616</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.44</v>
+        <v>-4.61</v>
       </c>
       <c r="L49" t="n">
-        <v>4.78</v>
+        <v>5.02</v>
       </c>
       <c r="M49" t="n">
         <v>1.39</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>7.45</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>670</v>
+        <v>646.05</v>
       </c>
       <c r="I50" t="n">
         <v>653.6859239298159</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K50" t="n">
-        <v>1.62</v>
+        <v>-2.01</v>
       </c>
       <c r="L50" t="n">
-        <v>1.3</v>
+        <v>2.02</v>
       </c>
       <c r="M50" t="n">
         <v>0.74</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.99</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45824.55208333334</v>
+        <v>45825.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>644.6</v>
+        <v>651.6</v>
       </c>
       <c r="I51" t="n">
         <v>650.8753778176459</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>39</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>0.22</v>
+        <v>-0.86</v>
       </c>
       <c r="L51" t="n">
         <v>8.27</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.16</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45849.38541666666</v>
+        <v>45849.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>656.85</v>
+        <v>653</v>
       </c>
       <c r="I52" t="n">
         <v>654.8627020284588</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="L52" t="n">
         <v>3.88</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>4.59</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45854.55208333334</v>
+        <v>45855.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>670.7</v>
+        <v>694.55</v>
       </c>
       <c r="I53" t="n">
         <v>682.9803623492214</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.71</v>
+        <v>-6.36</v>
       </c>
       <c r="L53" t="n">
-        <v>3.68</v>
+        <v>6.81</v>
       </c>
       <c r="M53" t="n">
-        <v>0.15</v>
+        <v>0.34</v>
       </c>
       <c r="N53" t="n">
-        <v>1.78</v>
+        <v>3.27</v>
       </c>
       <c r="O53" t="n">
         <v>-1.14</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.27</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45870.38541666666</v>
+        <v>45870.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>707.1</v>
+        <v>660</v>
       </c>
       <c r="I54" t="n">
         <v>698.5453520522456</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>1.81</v>
+        <v>-4.97</v>
       </c>
       <c r="L54" t="n">
-        <v>3.46</v>
+        <v>5.26</v>
       </c>
       <c r="M54" t="n">
         <v>0.9399999999999999</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.32</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45891.55208333334</v>
+        <v>45894.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>713.7</v>
+        <v>730.65</v>
       </c>
       <c r="I55" t="n">
         <v>720.6195015146295</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-8.140000000000001</v>
+        <v>-10.7</v>
       </c>
       <c r="L55" t="n">
-        <v>10.65</v>
+        <v>12.27</v>
       </c>
       <c r="M55" t="n">
         <v>2.05</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.58</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45904.55208333334</v>
+        <v>45905.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>696</v>
+        <v>686.6</v>
       </c>
       <c r="I56" t="n">
         <v>689.9040323254155</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.74</v>
+        <v>-6.03</v>
       </c>
       <c r="L56" t="n">
-        <v>5.29</v>
+        <v>6.36</v>
       </c>
       <c r="M56" t="n">
         <v>0.41</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.86</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>676</v>
+        <v>677.65</v>
       </c>
       <c r="I57" t="n">
         <v>677.4147333736013</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K57" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="L57" t="n">
         <v>4.27</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.84</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45985.38541666666</v>
+        <v>45985.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>744.55</v>
+        <v>737.3</v>
       </c>
       <c r="I58" t="n">
         <v>740.2987915551503</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>9.869999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L58" t="n">
         <v>1.72</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>4.17</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>749.2</v>
+        <v>776.75</v>
       </c>
       <c r="I59" t="n">
         <v>768.0187810793351</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>25</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.61</v>
+        <v>-5.35</v>
       </c>
       <c r="L59" t="n">
-        <v>4.37</v>
+        <v>5.57</v>
       </c>
       <c r="M59" t="n">
         <v>0.78</v>
       </c>
       <c r="N59" t="n">
-        <v>2.6</v>
+        <v>3.91</v>
       </c>
       <c r="O59" t="n">
         <v>-1.5</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.17</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46031.38541666666</v>
+        <v>46031.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>781.7</v>
+        <v>770.5</v>
       </c>
       <c r="I60" t="n">
         <v>774.3013050869571</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>0.64</v>
+        <v>-0.8</v>
       </c>
       <c r="L60" t="n">
         <v>3.17</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.18</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46056.38541666666</v>
+        <v>46056.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>736.8</v>
+        <v>739.9</v>
       </c>
       <c r="I61" t="n">
         <v>737.1815350678703</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>24.83333333333333</v>
+        <v>25</v>
       </c>
       <c r="K61" t="n">
-        <v>4.37</v>
+        <v>3.97</v>
       </c>
       <c r="L61" t="n">
         <v>3.84</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>10.2</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46073.55208333334</v>
+        <v>46076.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>751.5</v>
+        <v>640.25</v>
       </c>
       <c r="I62" t="n">
         <v>725.3576320967223</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>1.57</v>
+        <v>-13.47</v>
       </c>
       <c r="L62" t="n">
-        <v>3.18</v>
+        <v>15.45</v>
       </c>
       <c r="M62" t="n">
-        <v>0.67</v>
+        <v>4.89</v>
       </c>
       <c r="N62" t="n">
-        <v>2.82</v>
+        <v>14.17</v>
       </c>
       <c r="O62" t="n">
         <v>6.13</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>16.47</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>606.35</v>
+        <v>637.4</v>
       </c>
       <c r="I63" t="n">
         <v>614.8737698953497</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K63" t="n">
-        <v>5.29</v>
+        <v>0.45</v>
       </c>
       <c r="L63" t="n">
         <v>11.64</v>
       </c>
       <c r="M63" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="N63" t="n">
-        <v>5.22</v>
+        <v>6.04</v>
       </c>
       <c r="O63" t="n">
         <v>-14.17</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.5</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>639.25</v>
+        <v>627.1</v>
       </c>
       <c r="I64" t="n">
         <v>628.6913396861288</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K64" t="n">
-        <v>0.29</v>
+        <v>-1.62</v>
       </c>
       <c r="L64" t="n">
         <v>3.51</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>589</v>
+        <v>606</v>
       </c>
       <c r="I65" t="n">
         <v>594.6556075085031</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>51</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K65" t="n">
-        <v>6.08</v>
+        <v>3.36</v>
       </c>
       <c r="L65" t="n">
         <v>5.5</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.36</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46237.55208333334</v>
+        <v>46238.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>621.4</v>
+        <v>585.3</v>
       </c>
       <c r="I66" t="n">
         <v>593.6121326190201</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K66" t="n">
-        <v>2.54</v>
+        <v>-3.42</v>
       </c>
       <c r="L66" t="n">
         <v>5.03</v>
@@ -4203,7 +4994,7 @@
         <v>0.63</v>
       </c>
       <c r="N66" t="n">
-        <v>3.12</v>
+        <v>6.36</v>
       </c>
       <c r="O66" t="n">
         <v>3.06</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46259.38541666666</v>
+        <v>46259.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>572.85</v>
+        <v>582.2</v>
       </c>
       <c r="I67" t="n">
         <v>580.2254982222555</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>2.13</v>
+        <v>0.53</v>
       </c>
       <c r="L67" t="n">
         <v>5.87</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>4.28</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46265.38541666666</v>
+        <v>46265.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>566.75</v>
+        <v>563.3</v>
       </c>
       <c r="I68" t="n">
         <v>563.7992702530233</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.65</v>
+        <v>-3.25</v>
       </c>
       <c r="L68" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="M68" t="n">
         <v>0.44</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>3.84</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46268.55208333334</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>581</v>
+        <v>586.65</v>
       </c>
       <c r="I69" t="n">
         <v>584.624664869145</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.14</v>
+        <v>-4.15</v>
       </c>
       <c r="L69" t="n">
-        <v>4.06</v>
+        <v>4.63</v>
       </c>
       <c r="M69" t="n">
         <v>0.77</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>4.3</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46280.38541666666</v>
+        <v>46280.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>566.9</v>
+        <v>558.1</v>
       </c>
       <c r="I70" t="n">
         <v>563.0601416772766</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.37</v>
+        <v>-4.87</v>
       </c>
       <c r="L70" t="n">
-        <v>3.74</v>
+        <v>4.88</v>
       </c>
       <c r="M70" t="n">
         <v>1.02</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>4.6</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46307.38541666666</v>
+        <v>46307.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>502</v>
+        <v>514.35</v>
       </c>
       <c r="I71" t="n">
         <v>511.783454544297</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>26.83333333333333</v>
+        <v>27</v>
       </c>
       <c r="K71" t="n">
-        <v>10.05</v>
+        <v>7.84</v>
       </c>
       <c r="L71" t="n">
         <v>1.99</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>7.14</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>526.15</v>
+        <v>510.35</v>
       </c>
       <c r="I72" t="n">
         <v>510.9726922281902</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K72" t="n">
-        <v>2.29</v>
+        <v>-0.78</v>
       </c>
       <c r="L72" t="n">
         <v>2.4</v>
@@ -4545,7 +5408,7 @@
         <v>0.89</v>
       </c>
       <c r="N72" t="n">
-        <v>2</v>
+        <v>2.59</v>
       </c>
       <c r="O72" t="n">
         <v>4.96</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,12 @@
       <c r="Q73" t="n">
         <v>10</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6707,7 +7588,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="6">
@@ -6717,7 +7598,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -6727,7 +7608,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="8">
@@ -6737,7 +7618,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -6747,7 +7628,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.6</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="10">
@@ -6757,7 +7638,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="11">
@@ -6767,7 +7648,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -6777,7 +7658,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6787,7 +7668,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71.8</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -6797,7 +7678,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.99</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="15">
@@ -6807,7 +7688,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.07</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="16">
@@ -6817,7 +7698,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.91</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="17">
@@ -6827,7 +7708,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16.34</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="18">
@@ -6837,7 +7718,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60.6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6847,7 +7728,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.77</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="20">
@@ -6857,7 +7738,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.46</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="21">
@@ -6867,7 +7748,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.64</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="22">
@@ -6877,7 +7758,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -6887,7 +7768,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -6897,7 +7778,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="25">
@@ -6917,7 +7798,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.03</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="27">
@@ -6927,7 +7808,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.7</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="28">
@@ -6937,7 +7818,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
